--- a/web/files/港岛-半山区西部-天御第2期.xlsx
+++ b/web/files/港岛-半山区西部-天御第2期.xlsx
@@ -126,7 +126,8 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -274,7 +275,7 @@
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1611,7 +1612,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1742,7 +1743,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -1817,7 +1818,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1883,7 +1884,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1949,7 +1950,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -2015,7 +2016,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -2081,7 +2082,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2147,7 +2148,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2213,7 +2214,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2279,7 +2280,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2345,7 +2346,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2411,7 +2412,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2477,7 +2478,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2543,7 +2544,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2609,7 +2610,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2675,7 +2676,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2741,7 +2742,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2807,7 +2808,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2873,7 +2874,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2939,7 +2940,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -3005,7 +3006,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -3071,7 +3072,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -3137,7 +3138,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3203,7 +3204,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3269,7 +3270,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3335,7 +3336,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3401,7 +3402,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3467,7 +3468,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3533,7 +3534,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -5323,12 +5324,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -5652,7 +5653,7 @@
           <t>- | 5470呎 (4+房)
 $42291万
 $77,315/呎
-(26年-02月-04日)</t>
+(26年-02月-05日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr"/>
@@ -5694,7 +5695,7 @@
           <t>- | 5590呎 (3房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr"/>
@@ -5715,7 +5716,7 @@
           <t>- | 5483呎 (3房)
 $37361万
 $68,140/呎
-(26年-06月-10日)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr"/>
@@ -5737,7 +5738,7 @@
           <t>A | 2727呎 (4+房)
 $16133万
 $59,161/呎
-(25年-11月-17日)</t>
+(25年-11月-18日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -5745,7 +5746,7 @@
           <t>B | 2723呎 (4+房)
 $15778万
 $57,945/呎
-(25年-11月-17日)</t>
+(25年-11月-18日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr"/>
@@ -5765,7 +5766,7 @@
           <t>A | 2727呎 (4+房)
 $15580万
 $57,132/呎
-(26年-02月-10日)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -5773,7 +5774,7 @@
           <t>B | 2723呎 (4+房)
 $16469万
 $60,480/呎
-(26年-03月-30日)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr"/>
@@ -5793,7 +5794,7 @@
           <t>A | 2727呎 (4+房)
 $15809万
 $57,971/呎
-(26年-02月-10日)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -5801,7 +5802,7 @@
           <t>B | 2773呎 (4+房)
 $14956万
 $53,933/呎
-(26年-02月-22日)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr"/>
@@ -5821,7 +5822,7 @@
           <t>A | 2727呎 (4+房)
 $15410万
 $56,509/呎
-(26年-02月-05日)</t>
+(26年-02月-06日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -5829,7 +5830,7 @@
           <t>B | 2723呎 (4+房)
 $14778万
 $54,271/呎
-(26年-02月-26日)</t>
+(26年-02月-27日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr"/>
@@ -5849,7 +5850,7 @@
           <t>A | 2727呎 (4+房)
 $15071万
 $55,267/呎
-(26年-03月-02日)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -5857,7 +5858,7 @@
           <t>B | 2723呎 (4+房)
 $15194万
 $55,798/呎
-(25年-12月-10日)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr"/>
@@ -5877,7 +5878,7 @@
           <t>A | 2716呎 (4+房)
 $14934万
 $54,985/呎
-(25年-12月-03日)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -5885,7 +5886,7 @@
           <t>B | 2723呎 (4+房)
 $14415万
 $52,938/呎
-(26年-01月-08日)</t>
+(26年-01月-09日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr"/>
@@ -5905,7 +5906,7 @@
           <t>A | 2716呎 (4+房)
 $13694万
 $50,419/呎
-(25年-12月-15日)</t>
+(25年-12月-16日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -5913,7 +5914,7 @@
           <t>B | 2723呎 (4+房)
 $14138万
 $51,921/呎
-(26年-01月-27日)</t>
+(26年-01月-28日)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr"/>
@@ -5933,7 +5934,7 @@
           <t>A | 2716呎 (4+房)
 $13583万
 $50,010/呎
-(26年-01月-28日)</t>
+(26年-01月-29日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -5941,7 +5942,7 @@
           <t>B | 2723呎 (4+房)
 $13394万
 $49,187/呎
-(25年-12月-11日)</t>
+(25年-12月-12日)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr"/>
@@ -5961,7 +5962,7 @@
           <t>A | 2716呎 (4+房)
 $14155万
 $52,115/呎
-(26年-02月-08日)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -5969,7 +5970,7 @@
           <t>B | 2723呎 (4+房)
 $13583万
 $49,883/呎
-(25年-12月-15日)</t>
+(25年-12月-16日)</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr"/>
@@ -5989,7 +5990,7 @@
           <t>A | 2716呎 (4+房)
 $14150万
 $52,099/呎
-(26年-03月-15日)</t>
+(26年-03月-16日)</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -5997,7 +5998,7 @@
           <t>B | 2723呎 (4+房)
 $13638万
 $50,084/呎
-(26年-02月-11日)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="E30" s="20" t="inlineStr"/>
@@ -6017,7 +6018,7 @@
           <t>A | 2716呎 (4+房)
 $13272万
 $48,865/呎
-(26年-02月-11日)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -6025,7 +6026,7 @@
           <t>B | 2723呎 (4+房)
 $13183万
 $48,413/呎
-(26年-02月-11日)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr"/>
@@ -6045,7 +6046,7 @@
           <t>A | 2716呎 (4+房)
 $12973万
 $47,765/呎
-(26年-03月-03日)</t>
+(26年-03月-04日)</t>
         </is>
       </c>
       <c r="D32" s="22" t="inlineStr">
@@ -6053,7 +6054,7 @@
           <t>B | 2723呎 (4+房)
 $14162万
 $52,010/呎
-(26年-04月-13日)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr"/>
@@ -6073,7 +6074,7 @@
           <t>A | 2716呎 (4+房)
 $12923万
 $47,581/呎
-(26年-03月-26日)</t>
+(26年-03月-27日)</t>
         </is>
       </c>
       <c r="D33" s="22" t="inlineStr">
@@ -6081,7 +6082,7 @@
           <t>B | 2723呎 (4+房)
 $12859万
 $47,223/呎
-(26年-01月-14日)</t>
+(26年-01月-15日)</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr"/>

--- a/web/files/港岛-半山区西部-天御第2期.xlsx
+++ b/web/files/港岛-半山区西部-天御第2期.xlsx
@@ -126,8 +126,7 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
+      <color rgb="00002060"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -275,7 +274,7 @@
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1743,7 +1742,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -5324,12 +5323,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -5695,7 +5694,7 @@
           <t>- | 5590呎 (3房)
 招标单位
 -
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr"/>

--- a/web/files/港岛-半山区西部-天御第2期.xlsx
+++ b/web/files/港岛-半山区西部-天御第2期.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -129,6 +129,12 @@
       <color rgb="00002060"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -206,7 +212,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -275,6 +281,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1742,7 +1751,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -5689,12 +5698,12 @@
           <t>37</t>
         </is>
       </c>
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
         <is>
           <t>- | 5590呎 (3房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr"/>

--- a/web/files/港岛-半山区西部-天御第2期.xlsx
+++ b/web/files/港岛-半山区西部-天御第2期.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -126,11 +126,6 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00004D00"/>
       <sz val="8"/>
@@ -212,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -280,10 +275,7 @@
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5332,12 +5324,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -5698,7 +5690,7 @@
           <t>37</t>
         </is>
       </c>
-      <c r="B19" s="24" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>- | 5590呎 (3房)
 招标单位

--- a/web/files/港岛-半山区西部-天御第2期.xlsx
+++ b/web/files/港岛-半山区西部-天御第2期.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -124,12 +124,6 @@
       <color rgb="00660000"/>
       <sz val="8"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="8"/>
-    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -207,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -273,9 +267,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1743,23 +1734,19 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>408690000</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>73111</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1768,12 +1755,12 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
@@ -1783,7 +1770,7 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -5324,7 +5311,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -5334,7 +5321,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -5690,12 +5677,12 @@
           <t>37</t>
         </is>
       </c>
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>- | 5590呎 (3房)
-招标单位
--
-(在售)</t>
+$40869万
+$73,111/呎
+(26年-08月-19日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr"/>
